--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_rf_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_rf_quarterly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,27 +918,27 @@
         <v>1.292717059264024</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1040,35 +1041,35 @@
         <v>0.798509113087996</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
@@ -1076,15 +1077,15 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -1189,51 +1190,51 @@
         <v>0.8975818933077144</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1342,59 +1343,59 @@
         <v>0.7985091130879964</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AP6" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AR6" s="3" t="n">
@@ -1402,15 +1403,15 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AT6" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
     </row>
@@ -1509,51 +1510,51 @@
         <v>1.741554662338135</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1662,59 +1663,59 @@
         <v>1.26954572899565</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AP8" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AR8" s="3" t="n">
@@ -1722,15 +1723,15 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AT8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
     </row>
@@ -1829,51 +1830,51 @@
         <v>0.7839334519359051</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -1982,59 +1983,59 @@
         <v>1.159632812276755</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH10" s="3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AP10" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AR10" s="3" t="n">
@@ -2042,15 +2043,15 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AT10" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
     </row>
@@ -2349,66 +2350,68 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="M2" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.4859401977791229</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="P2" t="n">
-        <v>1895</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.265757517207872</v>
+        <v>0.09032004823014436</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.265757517207872</v>
+        <v>0.04076898034342898</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>-0.03939252582908825</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X2" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.4859401977791229</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.9452989626493455</v>
+        <v>0.2044255219913531</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -2456,34 +2459,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>37538</v>
+        <v>36038</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>39065</v>
+        <v>36104</v>
       </c>
       <c r="M3" t="n">
-        <v>1692</v>
+        <v>78</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.4893559340541901</v>
+        <v>-0.1757126481189499</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.4938733180213994</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="P3" t="n">
-        <v>1687</v>
+        <v>76</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.2282498761985527</v>
+        <v>0.09273364184105239</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.2156281040292364</v>
+        <v>0.03988750979864978</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -2493,29 +2496,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.4893559340541901</v>
+        <v>-0.1757126481189499</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.4938733180213994</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1054</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.9583112126208886</v>
+        <v>0.213169166939136</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -2571,34 +2576,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>38012</v>
+        <v>36104</v>
       </c>
       <c r="M4" t="n">
-        <v>963</v>
+        <v>78</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2928258101948606</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="P4" t="n">
-        <v>813</v>
+        <v>77</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1378626392028849</v>
+        <v>0.08652899115469197</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.0982768979428859</v>
+        <v>0.03721870417281659</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -2608,38 +2613,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X4" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2928258101948606</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>380</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4140787579868381</v>
+        <v>0.1932346188529419</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.1173512060863505</v>
+        <v>-0.002668805625833194</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.1965301238593294</v>
+        <v>0.01377080047234158</v>
       </c>
       <c r="AH4" t="n">
-        <v>-674</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -2694,34 +2701,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>36893</v>
+        <v>36038</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>38957</v>
+        <v>36510</v>
       </c>
       <c r="M5" t="n">
-        <v>1616</v>
+        <v>358</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1686386036366925</v>
+        <v>-0.1757126481189499</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1759931954029403</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="P5" t="n">
-        <v>1611</v>
+        <v>356</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.1204829958030841</v>
+        <v>0.1119924253493049</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.1112364453560276</v>
+        <v>0.1026885299639315</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -2731,38 +2738,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>196</v>
+        <v>31</v>
       </c>
       <c r="X5" t="n">
-        <v>-442</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1686386036366925</v>
+        <v>-0.1757126481189499</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1759931954029403</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1420</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>272</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2028463245640009</v>
+        <v>0.213169166939136</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1043916586732088</v>
+        <v>0.06280102016528177</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.3207173304174976</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>366</v>
+        <v>280</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -2821,34 +2830,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>39013</v>
+        <v>36104</v>
       </c>
       <c r="M6" t="n">
-        <v>1655</v>
+        <v>78</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.408153702506911</v>
+        <v>-0.1757126481189499</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.4133894374417633</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="P6" t="n">
-        <v>1650</v>
+        <v>76</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1973827596786266</v>
+        <v>0.09162253334985861</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.1844190232389638</v>
+        <v>0.03940958884191845</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -2858,50 +2867,52 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X6" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.408153702506911</v>
+        <v>-0.1757126481189499</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4133894374417633</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1072</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.689627871688556</v>
+        <v>0.213169166939136</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.03120908079027254</v>
+        <v>-0.0004779209567313258</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.08120223154727912</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.08614212529607791</v>
+        <v>0.002190884669101868</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.1153278923120503</v>
+        <v>-0.01377080047234158</v>
       </c>
       <c r="AL6" t="n">
-        <v>692</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -2952,76 +2963,80 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37691</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>36257</v>
+      </c>
       <c r="M7" t="n">
-        <v>1896</v>
+        <v>181</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.6319878587144449</v>
+        <v>-0.1757126481189499</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.6352434573939332</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="P7" t="n">
-        <v>1892</v>
+        <v>179</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.4306480297379806</v>
+        <v>0.1064294040417689</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.4306480297379806</v>
+        <v>0.06948377203652364</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>-0.2788538504565274</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>742</v>
+        <v>31</v>
       </c>
       <c r="X7" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.6319878587144449</v>
+        <v>-0.1757126481189499</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.6352434573939332</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1154</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>150</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>95</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>1.717301653436647</v>
+        <v>0.213169166939136</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.2150199257087442</v>
+        <v>0.02959626223787386</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>-0.1426319246602548</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>103</v>
+      </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -3077,86 +3092,92 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>36104</v>
+      </c>
       <c r="M8" t="n">
-        <v>1896</v>
+        <v>78</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.5554505076287066</v>
+        <v>-0.1757126481189499</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.5593831896735858</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="P8" t="n">
-        <v>1892</v>
+        <v>76</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.3311172832992209</v>
+        <v>0.09162253334985861</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.3311172832992209</v>
+        <v>0.03940958884191845</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>1</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>-0.1081065859312282</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.5554505076287066</v>
+        <v>-0.1757126481189499</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.5593831896735858</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1258</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>1.249468320536935</v>
+        <v>0.213169166939136</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.1154891792699846</v>
+        <v>-0.0004779209567313258</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>-0.06609457357451654</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
       <c r="AI8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.232840385356335</v>
+        <v>0.002190884669101868</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.262624697433846</v>
-      </c>
-      <c r="AL8" t="inlineStr"/>
+        <v>-0.01377080047234158</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
       <c r="AM8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
@@ -3204,83 +3225,87 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>37438</v>
-      </c>
+        <v>35993</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>1896</v>
+        <v>90</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.4156280000976651</v>
+        <v>0</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.4394409730279956</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1837</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.2993237292212272</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.2993237292212272</v>
+        <v>0</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.1010420913069554</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>568</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-70</v>
+        <v>-31</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.4156280000976651</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.4394409730279956</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1328</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-55</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.7112387317789495</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.08369562519199089</v>
+        <v>-0.03988750979864978</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.07372793395652499</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0.1757126481189499</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-47</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.05843080957065849</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.05333835813334986</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3329,89 +3354,99 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>36104</v>
+      </c>
       <c r="M10" t="n">
-        <v>1896</v>
+        <v>78</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-0.5261181959452543</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-0.5369583225836583</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="P10" t="n">
-        <v>1874</v>
+        <v>77</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.2843128645289108</v>
+        <v>0.08652899115469197</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.2843128645289108</v>
+        <v>0.03721870417281659</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
       </c>
       <c r="U10" t="b">
-        <v>1</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>-0.01551890344216456</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X10" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.5261181959452543</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.5369583225836583</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>1.110230845420842</v>
+        <v>0.1932346188529419</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.06868476049967445</v>
+        <v>-0.002668805625833194</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>-0.03676226189106424</v>
-      </c>
-      <c r="AH10" t="inlineStr"/>
+        <v>0.01377080047234158</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
       <c r="AI10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.1860359665860249</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.2332923857503937</v>
-      </c>
-      <c r="AL10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
       <c r="AM10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AN10" s="3" t="n">
+        <v>0.05843080957065849</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>-0.01735760353059468</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3708,68 +3743,66 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.4862309442441406</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.4862309442441406</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.2658275917027504</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.2658275917027504</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.5035092528573126</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.5040024023286764</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.2354171526922728</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1562892258388244</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>-0.03993583465459472</v>
+      </c>
       <c r="W2" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.5035092528573126</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>860</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>1.014136226616542</v>
+        <v>0.94639982458421</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -3817,34 +3850,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>39065</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1691</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.4900454549092434</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.4938733180213996</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1688</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.2283173159625294</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.2156849604848136</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>41340</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1361</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.5638362806438034</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.5638362806438034</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1360</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.2483485089561435</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.174491493740388</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -3854,31 +3887,29 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.4900454549092434</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.4938733180213996</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1006</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>146</v>
-      </c>
+        <v>1054</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>1.292717059264028</v>
+        <v>0.9609590886615789</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -3934,34 +3965,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>38007</v>
+      </c>
+      <c r="M4" t="n">
+        <v>959</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.291230325563591</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.3309499985899496</v>
+      </c>
+      <c r="P4" t="n">
+        <v>796</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1381187240689723</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.09828087349740594</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>40746</v>
-      </c>
-      <c r="M4" t="n">
-        <v>954</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.4439839127181154</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.4439839127181154</v>
-      </c>
-      <c r="P4" t="n">
-        <v>953</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1982156637126214</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.1166175213781546</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -3971,40 +4002,38 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.291230325563591</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>599</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-261</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.798509113087996</v>
+        <v>0.410895578729674</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.05787397236223338</v>
+        <v>-0.1174040869874076</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.119852367925688</v>
+        <v>0.1988151293456525</v>
       </c>
       <c r="AH4" t="n">
-        <v>-407</v>
+        <v>-677</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4059,34 +4088,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>36893</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>38958</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1616</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1697611879554135</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1759931954029403</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1613</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1204830371904383</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.1112658142158614</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>41064</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>41401</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1403</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.2258101889952296</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.2593752373510614</v>
-      </c>
-      <c r="P5" t="n">
-        <v>470</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.09644544888272065</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.06880015907936661</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -4096,40 +4125,38 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>1172</v>
+        <v>195</v>
       </c>
       <c r="X5" t="n">
-        <v>817</v>
+        <v>-442</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2258101889952296</v>
+        <v>-0.1697611879554135</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2593752373510614</v>
+        <v>-0.1759931954029403</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>231</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-629</v>
-      </c>
+        <v>1421</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2916729021558233</v>
+        <v>0.204472719767643</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1056913346610214</v>
+        <v>-0.1044191462689522</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.3380260916485738</v>
+        <v>0.3202842669538299</v>
       </c>
       <c r="AH5" t="n">
-        <v>-775</v>
+        <v>367</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -4138,12 +4165,8 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.1285602973317337</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.09292888339844574</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4192,34 +4215,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>39013</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1654</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.4089528704446636</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.4133894374417632</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1651</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.197442382927133</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.1844676505366419</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1215</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.4439839127181154</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.4439839127181154</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1214</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1826986027075818</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.1212903259276406</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -4229,62 +4252,56 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.4089528704446636</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.4133894374417632</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>860</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
+        <v>1072</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.798509113087996</v>
+        <v>0.6919124550225493</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.05320116781274746</v>
+        <v>-0.03121730994817171</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.119852367925688</v>
+        <v>0.0810925844645799</v>
       </c>
       <c r="AH6" t="n">
-        <v>-146</v>
+        <v>18</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.004672804549485918</v>
+        <v>0.08618677703923591</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>0</v>
+        <v>-0.1177225448810726</v>
       </c>
       <c r="AL6" t="n">
-        <v>261</v>
+        <v>695</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.1285602973317337</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.003879815783991547</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4329,80 +4346,76 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>37691</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.6324847841919969</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.6352434573939333</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.430761582285699</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.430761582285699</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>40101</v>
-      </c>
-      <c r="M7" t="n">
-        <v>509</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.316876237017826</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.316876237017826</v>
-      </c>
-      <c r="P7" t="n">
-        <v>508</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1100150456604966</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.04730001964953569</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>-0.2798276115218413</v>
+      </c>
       <c r="W7" t="n">
-        <v>355</v>
+        <v>741</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.316876237017826</v>
+        <v>-0.6324847841919969</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.316876237017826</v>
+        <v>-0.6352434573939333</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>154</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-706</v>
-      </c>
+        <v>1154</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4638635840078291</v>
+        <v>1.720975777292494</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.1271914740908524</v>
+        <v>0.2150766218008854</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2469600436259775</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-852</v>
-      </c>
+        <v>-0.1424393292827535</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -4458,92 +4471,86 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.5560507812175628</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.5593831896735858</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.3312045917472245</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.3312045917472245</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>41165</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1243</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.4803090186007117</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.4803090186007117</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1242</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1926007533015539</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.1293279284982969</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>-0.1093109064168606</v>
+      </c>
       <c r="W8" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.4803090186007117</v>
+        <v>-0.5560507812175628</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.4803090186007117</v>
+        <v>-0.5593831896735858</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>888</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>28</v>
-      </c>
+        <v>1258</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.9242204228895043</v>
+        <v>1.252509876563297</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.04516356524209114</v>
+        <v>0.1155196312624109</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.08352726204309169</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-118</v>
-      </c>
+        <v>-0.06600532630831935</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.01271040712014224</v>
+        <v>0.2329237182498186</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.0363251058825963</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>289</v>
-      </c>
+        <v>-0.2648204556539718</v>
+      </c>
+      <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
@@ -4591,80 +4598,76 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>37438</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.4164170755181256</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.4394409730279956</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1840</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.2994026543983987</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.2994026543983987</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>40911</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>41390</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1396</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.1634954846035341</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.2290574595209739</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1206</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.11884481883854</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.0845673274153509</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>-0.1022559509544005</v>
+      </c>
       <c r="W9" t="n">
-        <v>1067</v>
+        <v>567</v>
       </c>
       <c r="X9" t="n">
-        <v>712</v>
+        <v>-70</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1634954846035341</v>
+        <v>-0.4164170755181256</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.2290574595209739</v>
+        <v>-0.4394409730279956</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>329</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-531</v>
-      </c>
+        <v>1328</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1954508094030365</v>
+        <v>0.7135525356363628</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.08992416632503712</v>
+        <v>0.08371769391358519</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.4003407960402693</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-677</v>
-      </c>
+        <v>0.07362837939111788</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -4720,92 +4723,86 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.5267580768496193</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.5369583225836583</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1877</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.2843878316665431</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.2843878316665431</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K10" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>41131</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1220</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.4564161498649841</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.4564161498649841</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1219</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.2005107799765412</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.1333889052146184</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T10" t="b">
         <v>0</v>
       </c>
       <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>-0.01684824474416335</v>
+      </c>
       <c r="W10" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.4564161498649841</v>
+        <v>-0.5267580768496193</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.4564161498649841</v>
+        <v>-0.5369583225836583</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>865</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>5</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.8396425864227186</v>
+        <v>1.113084135367764</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.04110258852576967</v>
+        <v>0.06870287118172952</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.1074201307788193</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-141</v>
-      </c>
+        <v>-0.03671262194037583</v>
+      </c>
+      <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.0167713838364637</v>
+        <v>0.1861069581691371</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.0124322371468687</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>266</v>
-      </c>
+        <v>-0.2355277512860283</v>
+      </c>
+      <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10" s="3" t="inlineStr"/>
       <c r="AO10" s="3" t="inlineStr"/>
@@ -5105,34 +5102,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>43570</v>
+        <v>41124</v>
       </c>
       <c r="M2" t="n">
-        <v>140</v>
+        <v>1215</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="P2" t="n">
-        <v>132</v>
+        <v>1213</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.08269444253856398</v>
+        <v>0.2354171526922728</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.05218963375687868</v>
+        <v>0.1563175570682493</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -5142,22 +5139,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -5166,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2429105460160748</v>
+        <v>1.014136226616542</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -5214,34 +5211,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>43501</v>
+        <v>41340</v>
       </c>
       <c r="M3" t="n">
-        <v>92</v>
+        <v>1361</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.1406317904810741</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="P3" t="n">
-        <v>81</v>
+        <v>1360</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.05204714860336933</v>
+        <v>0.2483485089561435</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.02667698748175109</v>
+        <v>0.1745231245742816</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -5251,31 +5248,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1406317904810741</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>28</v>
+        <v>1006</v>
       </c>
       <c r="AC3" t="n">
-        <v>-48</v>
+        <v>146</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.1636455583571095</v>
+        <v>1.292717059264028</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -5331,34 +5328,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43542</v>
+        <v>40746</v>
       </c>
       <c r="M4" t="n">
-        <v>120</v>
+        <v>954</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="P4" t="n">
-        <v>116</v>
+        <v>953</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04694464568316091</v>
+        <v>0.1982156637126214</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.02744587744229462</v>
+        <v>0.1166386611447342</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -5368,40 +5365,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>56</v>
+        <v>599</v>
       </c>
       <c r="AC4" t="n">
-        <v>-20</v>
+        <v>-261</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1600183179571426</v>
+        <v>0.798509113087996</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.0007688899605435319</v>
+        <v>-0.05788446342954737</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.002687142987107038</v>
+        <v>0.119852367925688</v>
       </c>
       <c r="AH4" t="n">
-        <v>28</v>
+        <v>-407</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -5456,34 +5453,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>43458</v>
+        <v>41064</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>43511</v>
+        <v>41401</v>
       </c>
       <c r="M5" t="n">
-        <v>100</v>
+        <v>1403</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1417910949420261</v>
+        <v>-0.2258101889952296</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1492975281333246</v>
+        <v>-0.2593752373510614</v>
       </c>
       <c r="P5" t="n">
-        <v>86</v>
+        <v>470</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.05025110994312699</v>
+        <v>0.09644544888272065</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.02684137222647894</v>
+        <v>0.06881263078418752</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -5493,40 +5490,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>64</v>
+        <v>1172</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>817</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1417910949420261</v>
+        <v>-0.2258101889952296</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1492975281333246</v>
+        <v>-0.2593752373510614</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>36</v>
+        <v>231</v>
       </c>
       <c r="AC5" t="n">
-        <v>-40</v>
+        <v>-629</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.165217459416187</v>
+        <v>0.2916729021558233</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.0001643847447278489</v>
+        <v>-0.105710493790094</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>-0.001159304460952026</v>
+        <v>0.3380260916485738</v>
       </c>
       <c r="AH5" t="n">
-        <v>8</v>
+        <v>-775</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -5536,10 +5533,10 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" s="3" t="n">
-        <v>0.148410030246944</v>
+        <v>0.1285602973317337</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.1211258743527557</v>
+        <v>-0.09292888339844574</v>
       </c>
     </row>
     <row r="6">
@@ -5589,34 +5586,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>43521</v>
+        <v>41124</v>
       </c>
       <c r="M6" t="n">
-        <v>105</v>
+        <v>1215</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1467474578207134</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="P6" t="n">
-        <v>101</v>
+        <v>1214</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.04911494966061319</v>
+        <v>0.1826986027075818</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.02687602304963537</v>
+        <v>0.1213123127538753</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -5626,61 +5623,61 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1467474578207134</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>41</v>
+        <v>860</v>
       </c>
       <c r="AC6" t="n">
-        <v>-35</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1719859602713949</v>
+        <v>0.798509113087996</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.000199035567884278</v>
+        <v>-0.05321081182040625</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>-0.006115667339639308</v>
+        <v>0.119852367925688</v>
       </c>
       <c r="AH6" t="n">
-        <v>13</v>
+        <v>-146</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>-0.0005698543926592539</v>
+        <v>0.004673651609141113</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.008802810326746346</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-15</v>
+        <v>261</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.148410030246944</v>
+        <v>0.1285602973317337</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>0.01497703503645686</v>
+        <v>-0.003879815783991547</v>
       </c>
     </row>
     <row r="7">
@@ -5726,34 +5723,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>43763</v>
+        <v>40101</v>
       </c>
       <c r="M7" t="n">
-        <v>275</v>
+        <v>509</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.1406317904810741</v>
+        <v>-0.316876237017826</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.316876237017826</v>
       </c>
       <c r="P7" t="n">
-        <v>264</v>
+        <v>508</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.06602383509600836</v>
+        <v>0.1100150456604966</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.05829800020352845</v>
+        <v>0.04730859393033657</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -5763,40 +5760,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1406317904810741</v>
+        <v>-0.316876237017826</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.316876237017826</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="AC7" t="n">
-        <v>135</v>
+        <v>-706</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.1636455583571095</v>
+        <v>0.4638635840078291</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.03162101272177736</v>
+        <v>-0.127214530643945</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0</v>
+        <v>0.2469600436259775</v>
       </c>
       <c r="AH7" t="n">
-        <v>183</v>
+        <v>-852</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -5855,34 +5852,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>43542</v>
+        <v>41165</v>
       </c>
       <c r="M8" t="n">
-        <v>120</v>
+        <v>1243</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1406317904810741</v>
+        <v>-0.4803090186007117</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.4803090186007117</v>
       </c>
       <c r="P8" t="n">
-        <v>109</v>
+        <v>1242</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.05088213746278813</v>
+        <v>0.1926007533015539</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.02974790603876255</v>
+        <v>0.1293513723357954</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -5892,52 +5889,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1406317904810741</v>
+        <v>-0.4803090186007117</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.4803090186007117</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>56</v>
+        <v>888</v>
       </c>
       <c r="AC8" t="n">
-        <v>-20</v>
+        <v>28</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1636455583571095</v>
+        <v>0.9242204228895043</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.00307091855701146</v>
+        <v>-0.04517175223848616</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
+        <v>0.08352726204309169</v>
       </c>
       <c r="AH8" t="n">
-        <v>28</v>
+        <v>-118</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.002302028596467928</v>
+        <v>0.01271271119106121</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.002687142987107038</v>
+        <v>-0.0363251058825963</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -5988,34 +5985,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43458</v>
+        <v>40911</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>43763</v>
+        <v>41390</v>
       </c>
       <c r="M9" t="n">
-        <v>275</v>
+        <v>1396</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1406317904810741</v>
+        <v>-0.1634954846035341</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.2290574595209739</v>
       </c>
       <c r="P9" t="n">
-        <v>264</v>
+        <v>1206</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.06602383509600836</v>
+        <v>0.11884481883854</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.05829800020352845</v>
+        <v>0.08458265730352456</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -6025,40 +6022,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>64</v>
+        <v>1067</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>712</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1406317904810741</v>
+        <v>-0.1634954846035341</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.2290574595209739</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>211</v>
+        <v>329</v>
       </c>
       <c r="AC9" t="n">
-        <v>135</v>
+        <v>-531</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1636455583571095</v>
+        <v>0.1954508094030365</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.03162101272177736</v>
+        <v>-0.08994046727075701</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0</v>
+        <v>0.4003407960402693</v>
       </c>
       <c r="AH9" t="n">
-        <v>183</v>
+        <v>-677</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -6117,34 +6114,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>43542</v>
+        <v>41131</v>
       </c>
       <c r="M10" t="n">
-        <v>120</v>
+        <v>1220</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-0.1406317904810741</v>
+        <v>-0.4564161498649841</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.4564161498649841</v>
       </c>
       <c r="P10" t="n">
-        <v>109</v>
+        <v>1219</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.05088213746278813</v>
+        <v>0.2005107799765412</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.02974790603876255</v>
+        <v>0.133413085203073</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -6154,52 +6151,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.1406317904810741</v>
+        <v>-0.4564161498649841</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.4564161498649841</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>56</v>
+        <v>865</v>
       </c>
       <c r="AC10" t="n">
-        <v>-20</v>
+        <v>5</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.1636455583571095</v>
+        <v>0.8396425864227186</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.00307091855701146</v>
+        <v>-0.04111003937120852</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0</v>
+        <v>0.1074201307788193</v>
       </c>
       <c r="AH10" t="n">
-        <v>28</v>
+        <v>-141</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.002302028596467928</v>
+        <v>0.01677442405833884</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.002687142987107038</v>
+        <v>-0.0124322371468687</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -6502,34 +6499,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43572</v>
+      </c>
+      <c r="M2" t="n">
+        <v>143</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.1989728318606708</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2022979914860072</v>
+      </c>
+      <c r="P2" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.08183226369428324</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05211846719049073</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>43992</v>
-      </c>
-      <c r="M2" t="n">
-        <v>78</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="P2" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1403286526425155</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.05728893254440421</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -6539,22 +6536,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606708</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -6563,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4088864968986545</v>
+        <v>0.2483971078320053</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -6611,34 +6608,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>43515</v>
+      </c>
+      <c r="M3" t="n">
+        <v>102</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1428942080320033</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1492975281333248</v>
+      </c>
+      <c r="P3" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.04978003260477074</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.02681387698071469</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>44069</v>
-      </c>
-      <c r="M3" t="n">
-        <v>132</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.3214421646736139</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.3214421646736139</v>
-      </c>
-      <c r="P3" t="n">
-        <v>131</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1317372817268568</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.06978231093443385</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -6648,31 +6645,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1428942080320033</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="AC3" t="n">
-        <v>54</v>
+        <v>-41</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4737137321817237</v>
+        <v>0.1667171186696854</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -6728,34 +6725,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>43539</v>
+      </c>
+      <c r="M4" t="n">
+        <v>120</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1373591481699221</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1410541034597296</v>
+      </c>
+      <c r="P4" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.04694462358448135</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.0274071811141844</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M4" t="n">
-        <v>122</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P4" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1167974844615735</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.05949724743333182</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -6765,40 +6762,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1373591481699221</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="AC4" t="n">
-        <v>44</v>
+        <v>-23</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1592309799362237</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.01028506350110202</v>
+        <v>0.0005933041334697173</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.03119568749080193</v>
+        <v>0.005535059862081138</v>
       </c>
       <c r="AH4" t="n">
-        <v>-10</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -6853,83 +6850,91 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>43511</v>
+      </c>
+      <c r="M5" t="n">
+        <v>101</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1417179384569855</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1492975281333249</v>
+      </c>
+      <c r="P5" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.05000417424753503</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.02680354081623767</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>473</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.3214421646736139</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.3214421646736139</v>
-      </c>
-      <c r="P5" t="n">
-        <v>473</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.2549969948320429</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.2549969948320429</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>1</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>-0.2580405485958912</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1417179384569855</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333249</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-42</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4737137321817237</v>
+        <v>0.1651181410015792</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.185214683897609</v>
+        <v>-1.033616447701502e-05</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>0.001176269575017708</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-1</v>
+      </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.1514413748399237</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.1235143586481885</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6978,34 +6983,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>43518</v>
+      </c>
+      <c r="M6" t="n">
+        <v>105</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1461679372768953</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1492975281333246</v>
+      </c>
+      <c r="P6" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.04911494966061309</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.02683814280100026</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>44075</v>
-      </c>
-      <c r="M6" t="n">
-        <v>136</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.3214421646736139</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.3214421646736139</v>
-      </c>
-      <c r="P6" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1428909433502804</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.07682026768293439</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -7015,58 +7020,62 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1461679372768953</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333246</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>113</v>
+        <v>40</v>
       </c>
       <c r="AC6" t="n">
-        <v>58</v>
+        <v>-38</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.4737137321817237</v>
+        <v>0.1711904994651121</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.007037956748500537</v>
+        <v>2.426582028557112e-05</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
+        <v>-0.003273729244891999</v>
       </c>
       <c r="AH6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.01732302024960256</v>
+        <v>-0.0005690383131841462</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.03119568749080193</v>
+        <v>-0.008808789106973136</v>
       </c>
       <c r="AL6" t="n">
-        <v>14</v>
+        <v>-15</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="n">
+        <v>0.1514413748399237</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>0.01161787289546434</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7111,34 +7120,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>43763</v>
+      </c>
+      <c r="M7" t="n">
+        <v>276</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1428942080320033</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1492975281333248</v>
+      </c>
+      <c r="P7" t="n">
+        <v>267</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.0659075900353976</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.0582185171530843</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>44389</v>
-      </c>
-      <c r="M7" t="n">
-        <v>351</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.3214421646736139</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.3214421646736139</v>
-      </c>
-      <c r="P7" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1977355589701255</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.1703989588315308</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -7148,40 +7157,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1428942080320033</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>328</v>
+        <v>211</v>
       </c>
       <c r="AC7" t="n">
-        <v>273</v>
+        <v>133</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4737137321817237</v>
+        <v>0.1667171186696854</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.1006166478970969</v>
+        <v>0.03140464017236962</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>219</v>
+        <v>174</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -7240,34 +7249,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>43542</v>
+      </c>
+      <c r="M8" t="n">
+        <v>121</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1428942080320033</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1492975281333248</v>
+      </c>
+      <c r="P8" t="n">
+        <v>112</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.05068214934192576</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.0297112390151239</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>44075</v>
-      </c>
-      <c r="M8" t="n">
-        <v>136</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.3214421646736139</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.3214421646736139</v>
-      </c>
-      <c r="P8" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1428909433502804</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.07682026768293439</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -7277,52 +7286,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1428942080320033</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>113</v>
+        <v>56</v>
       </c>
       <c r="AC8" t="n">
-        <v>58</v>
+        <v>-22</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4737137321817237</v>
+        <v>0.1667171186696854</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.007037956748500537</v>
+        <v>0.002897362034409216</v>
       </c>
       <c r="AG8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.01732302024960256</v>
+        <v>0.002304057900939498</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.03119568749080193</v>
+        <v>-0.005535059862081138</v>
       </c>
       <c r="AL8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -7373,76 +7382,80 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>43763</v>
+      </c>
+      <c r="M9" t="n">
+        <v>276</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.1428942080320033</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1492975281333248</v>
+      </c>
+      <c r="P9" t="n">
+        <v>267</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.0659075900353976</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.0582185171530843</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>473</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.3214421646736139</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.3214421646736139</v>
-      </c>
-      <c r="P9" t="n">
-        <v>473</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.2232011632533623</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.2232011632533623</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.1859520933418435</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1428942080320033</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>211</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>133</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.4737137321817237</v>
+        <v>0.1667171186696854</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.1534188523189285</v>
+        <v>0.03140464017236962</v>
       </c>
       <c r="AG9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr"/>
+      <c r="AH9" t="n">
+        <v>174</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -7498,34 +7511,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>43542</v>
+      </c>
+      <c r="M10" t="n">
+        <v>121</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.1428942080320033</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.1492975281333248</v>
+      </c>
+      <c r="P10" t="n">
+        <v>112</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.05068214934192576</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.0297112390151239</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>44075</v>
-      </c>
-      <c r="M10" t="n">
-        <v>136</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.3214421646736139</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.3214421646736139</v>
-      </c>
-      <c r="P10" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1428909433502804</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.07682026768293439</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -7535,52 +7548,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1428942080320033</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>113</v>
+        <v>56</v>
       </c>
       <c r="AC10" t="n">
-        <v>58</v>
+        <v>-22</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.4737137321817237</v>
+        <v>0.1667171186696854</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.007037956748500537</v>
+        <v>0.002897362034409216</v>
       </c>
       <c r="AG10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.01732302024960256</v>
+        <v>0.002304057900939498</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.03119568749080193</v>
+        <v>-0.005535059862081138</v>
       </c>
       <c r="AL10" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -7883,34 +7896,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43992</v>
+      </c>
+      <c r="M2" t="n">
+        <v>78</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="P2" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1403286526425155</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05728893254440421</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="M2" t="n">
-        <v>473</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.3239608533428744</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.3239608533428744</v>
-      </c>
-      <c r="P2" t="n">
-        <v>472</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1873955345996986</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1456175032694572</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -7920,22 +7933,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="X2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -7944,7 +7957,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4792042812088533</v>
+        <v>0.4088864968986545</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -7992,34 +8005,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="M3" t="n">
+        <v>132</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="P3" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1317372817268568</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.06978231093443385</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45092</v>
-      </c>
-      <c r="M3" t="n">
-        <v>364</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.3454801967968263</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.3454801967968263</v>
-      </c>
-      <c r="P3" t="n">
-        <v>363</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.215013307989909</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1466145071230273</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -8029,31 +8042,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3454801967968263</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3454801967968263</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>167</v>
+        <v>109</v>
       </c>
       <c r="AC3" t="n">
-        <v>-53</v>
+        <v>54</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.5278376530489537</v>
+        <v>0.4737137321817237</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -8109,34 +8122,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="M4" t="n">
+        <v>122</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="P4" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1167974844615735</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.05949724743333182</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45131</v>
-      </c>
-      <c r="M4" t="n">
-        <v>389</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2376608476183659</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2376608476183659</v>
-      </c>
-      <c r="P4" t="n">
-        <v>388</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1306673287628706</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.09210103019783453</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -8146,40 +8159,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="AC4" t="n">
-        <v>-26</v>
+        <v>44</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.3117521209239831</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.05451347692519282</v>
+        <v>-0.01028506350110202</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.1078193491784604</v>
+        <v>0.03119568749080193</v>
       </c>
       <c r="AH4" t="n">
-        <v>27</v>
+        <v>-10</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8234,91 +8247,83 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>473</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="P5" t="n">
+        <v>473</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.2549969948320429</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.2549969948320429</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>45226</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>45456</v>
-      </c>
-      <c r="M5" t="n">
-        <v>614</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.289736820923054</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.3016712444576485</v>
-      </c>
-      <c r="P5" t="n">
-        <v>551</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.2111895839787786</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.1869283722433472</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>-0.2580405485958912</v>
+      </c>
       <c r="W5" t="n">
-        <v>457</v>
+        <v>23</v>
       </c>
       <c r="X5" t="n">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.289736820923054</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3016712444576485</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>157</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-63</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4079288205529594</v>
+        <v>0.4737137321817237</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.04031386512031984</v>
+        <v>0.185214683897609</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.05574337587377232</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.8421981963585632</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.4564389497245325</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8367,34 +8372,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>44075</v>
+      </c>
+      <c r="M6" t="n">
+        <v>136</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="P6" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1428909433502804</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.07682026768293439</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45352</v>
-      </c>
-      <c r="M6" t="n">
-        <v>542</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.3188770471454476</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.3188770471454476</v>
-      </c>
-      <c r="P6" t="n">
-        <v>541</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.2015229411827191</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.1676060068844842</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -8404,62 +8409,58 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3188770471454476</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3188770471454476</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>345</v>
+        <v>113</v>
       </c>
       <c r="AC6" t="n">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.468163707901855</v>
+        <v>0.4737137321817237</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.02099149976145681</v>
+        <v>0.007037956748500537</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.02660314965137867</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>178</v>
+        <v>4</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.07550497668664963</v>
+        <v>0.01732302024960256</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.0812161995270817</v>
+        <v>-0.03119568749080193</v>
       </c>
       <c r="AL6" t="n">
-        <v>151</v>
+        <v>14</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.8421981963585632</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.08861411629547622</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8504,34 +8505,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>44389</v>
+      </c>
+      <c r="M7" t="n">
+        <v>351</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="P7" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1977355589701255</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.1703989588315308</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>44628</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45064</v>
-      </c>
-      <c r="M7" t="n">
-        <v>345</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.1811837223339979</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.1811837223339979</v>
-      </c>
-      <c r="P7" t="n">
-        <v>344</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.07506336184166679</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.04983462931104223</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -8541,40 +8542,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="X7" t="n">
-        <v>-151</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1811837223339979</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1811837223339979</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="AC7" t="n">
-        <v>81</v>
+        <v>273</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.22127518379392</v>
+        <v>0.4737137321817237</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.0967798778119851</v>
+        <v>0.1006166478970969</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1642964744628284</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>134</v>
+        <v>219</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -8633,34 +8634,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>44075</v>
+      </c>
+      <c r="M8" t="n">
+        <v>136</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="P8" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1428909433502804</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.07682026768293439</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45092</v>
-      </c>
-      <c r="M8" t="n">
-        <v>364</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.2682882916008086</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.2682882916008086</v>
-      </c>
-      <c r="P8" t="n">
-        <v>363</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1675930428997102</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.1142793049030369</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -8670,52 +8671,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.2682882916008086</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.2682882916008086</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>169</v>
+        <v>113</v>
       </c>
       <c r="AC8" t="n">
-        <v>-51</v>
+        <v>58</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.3666584646947342</v>
+        <v>0.4737137321817237</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.03233520221999041</v>
+        <v>0.007037956748500537</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.07719190519601771</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.02217827470520241</v>
+        <v>0.01732302024960256</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.03062744398244266</v>
+        <v>-0.03119568749080193</v>
       </c>
       <c r="AL8" t="n">
-        <v>-25</v>
+        <v>14</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -8766,87 +8767,83 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+        <v>43880</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43913</v>
+      </c>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>513</v>
+        <v>473</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.001622802338923757</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.09226300542917365</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>473</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.01496998077824432</v>
+        <v>0.2232011632533623</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>0.2232011632533623</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
         <v>1</v>
       </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
+      <c r="V9" s="3" t="n">
+        <v>-0.1859520933418435</v>
+      </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="X9" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.001622802338923757</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>0</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-220</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0</v>
+        <v>0.4737137321817237</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.1466145071230273</v>
+        <v>0.1534188523189285</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.3438573944579025</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-167</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="n">
-        <v>0.1149306197576361</v>
-      </c>
-      <c r="AO9" s="3" t="n">
-        <v>-0.1029587147715519</v>
-      </c>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8895,34 +8892,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>44075</v>
+      </c>
+      <c r="M10" t="n">
+        <v>136</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="P10" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.1428909433502804</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.07682026768293439</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45124</v>
-      </c>
-      <c r="M10" t="n">
-        <v>384</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2376608476183659</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.2376608476183659</v>
-      </c>
-      <c r="P10" t="n">
-        <v>383</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1314887237303285</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.09208397247949054</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -8932,62 +8929,58 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>189</v>
+        <v>113</v>
       </c>
       <c r="AC10" t="n">
-        <v>-31</v>
+        <v>58</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.3117521209239831</v>
+        <v>0.4737137321817237</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.0545305346435368</v>
+        <v>0.007037956748500537</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.1078193491784604</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>-1.70577183439824e-05</v>
+        <v>0.01732302024960256</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>0</v>
+        <v>-0.03119568749080193</v>
       </c>
       <c r="AL10" t="n">
-        <v>-5</v>
+        <v>14</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.1149306197576361</v>
-      </c>
-      <c r="AO10" s="3" t="n">
-        <v>-0.01368747521540192</v>
-      </c>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9284,34 +9277,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="M2" t="n">
+        <v>473</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.3239608533428744</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.3239608533428744</v>
+      </c>
+      <c r="P2" t="n">
+        <v>472</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1873955345996986</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.1456175032694572</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45835</v>
-      </c>
-      <c r="M2" t="n">
-        <v>89</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="P2" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1032426212645815</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.06633642004451831</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -9321,22 +9314,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428744</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428744</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -9345,7 +9338,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2889940469367012</v>
+        <v>0.4792042812088533</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -9393,34 +9386,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45092</v>
+      </c>
+      <c r="M3" t="n">
+        <v>364</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3454801967968263</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3454801967968263</v>
+      </c>
+      <c r="P3" t="n">
+        <v>363</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.215013307989909</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.1466145071230273</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45861</v>
-      </c>
-      <c r="M3" t="n">
-        <v>106</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.2051728224903451</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.2051728224903451</v>
-      </c>
-      <c r="P3" t="n">
-        <v>105</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.09605815620571079</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.06729733840789669</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -9430,31 +9423,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>34</v>
+        <v>197</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.3454801967968263</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.3454801967968263</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="AC3" t="n">
-        <v>17</v>
+        <v>-53</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.2581351371667873</v>
+        <v>0.5278376530489537</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -9510,34 +9503,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45131</v>
+      </c>
+      <c r="M4" t="n">
+        <v>389</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="P4" t="n">
+        <v>388</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1306673287628706</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.09210103019783453</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="M4" t="n">
-        <v>136</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="P4" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.06348808787815403</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.05032969331821049</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -9547,40 +9540,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>102</v>
+        <v>194</v>
       </c>
       <c r="AC4" t="n">
-        <v>47</v>
+        <v>-26</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1822068127687015</v>
+        <v>0.3117521209239831</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.0169676450896862</v>
+        <v>-0.05451347692519282</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.05104850955225826</v>
+        <v>0.1078193491784604</v>
       </c>
       <c r="AH4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -9635,73 +9628,77 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45456</v>
+      </c>
+      <c r="M5" t="n">
+        <v>614</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.289736820923054</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.3016712444576485</v>
+      </c>
+      <c r="P5" t="n">
+        <v>551</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.2111895839787786</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.1869283722433472</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>88</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="X5" t="n">
-        <v>-34</v>
+        <v>262</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0.289736820923054</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0.3016712444576485</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="AC5" t="n">
-        <v>-55</v>
+        <v>-63</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0</v>
+        <v>0.4079288205529594</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.06729733840789669</v>
+        <v>0.04031386512031984</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.2051728224903451</v>
+        <v>0.05574337587377232</v>
       </c>
       <c r="AH5" t="n">
-        <v>-72</v>
+        <v>-10</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -9711,10 +9708,10 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" s="3" t="n">
-        <v>0.1157245680572492</v>
+        <v>0.8421981963585632</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.08904827568122387</v>
+        <v>-0.4564389497245325</v>
       </c>
     </row>
     <row r="6">
@@ -9764,34 +9761,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45352</v>
+      </c>
+      <c r="M6" t="n">
+        <v>542</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3188770471454476</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3188770471454476</v>
+      </c>
+      <c r="P6" t="n">
+        <v>541</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.2015229411827191</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.1676060068844842</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="M6" t="n">
-        <v>136</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="P6" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.06348808787815403</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.05032969331821049</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -9801,61 +9798,61 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>34</v>
+        <v>197</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.3188770471454476</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.3188770471454476</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>102</v>
+        <v>345</v>
       </c>
       <c r="AC6" t="n">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1822068127687015</v>
+        <v>0.468163707901855</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.0169676450896862</v>
+        <v>0.02099149976145681</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.05104850955225826</v>
+        <v>0.02660314965137867</v>
       </c>
       <c r="AH6" t="n">
-        <v>30</v>
+        <v>178</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0</v>
+        <v>0.07550497668664963</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>0</v>
+        <v>-0.0812161995270817</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.1157245680572492</v>
+        <v>0.8421981963585632</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>-0.005987636340689106</v>
+        <v>-0.08861411629547622</v>
       </c>
     </row>
     <row r="7">
@@ -9901,73 +9898,77 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>44628</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45064</v>
+      </c>
+      <c r="M7" t="n">
+        <v>345</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1811837223339979</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1811837223339979</v>
+      </c>
+      <c r="P7" t="n">
+        <v>344</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.07506336184166679</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.04983462931104223</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" t="n">
-        <v>88</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="X7" t="n">
-        <v>-34</v>
+        <v>-151</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0</v>
+        <v>-0.1811837223339979</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0</v>
+        <v>-0.1811837223339979</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="AC7" t="n">
-        <v>-55</v>
+        <v>81</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0</v>
+        <v>0.22127518379392</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.06729733840789669</v>
+        <v>-0.0967798778119851</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2051728224903451</v>
+        <v>0.1642964744628284</v>
       </c>
       <c r="AH7" t="n">
-        <v>-72</v>
+        <v>134</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -9976,12 +9977,8 @@
       <c r="AK7" s="3" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" s="3" t="n">
-        <v>0.02141983290559235</v>
-      </c>
-      <c r="AO7" s="3" t="n">
-        <v>-0.01602903048447502</v>
-      </c>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10030,34 +10027,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45092</v>
+      </c>
+      <c r="M8" t="n">
+        <v>364</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.2682882916008086</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.2682882916008086</v>
+      </c>
+      <c r="P8" t="n">
+        <v>363</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1675930428997102</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.1142793049030369</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45866</v>
-      </c>
-      <c r="M8" t="n">
-        <v>109</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="P8" t="n">
-        <v>108</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.06821577159885669</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.0484565948035845</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -10067,62 +10064,58 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2682882916008086</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2682882916008086</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>75</v>
+        <v>169</v>
       </c>
       <c r="AC8" t="n">
-        <v>20</v>
+        <v>-51</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1822068127687015</v>
+        <v>0.3666584646947342</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.01884074360431218</v>
+        <v>-0.03233520221999041</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.05104850955225826</v>
+        <v>0.07719190519601771</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>-0.001873098514625984</v>
+        <v>0.02217827470520241</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>0</v>
+        <v>-0.03062744398244266</v>
       </c>
       <c r="AL8" t="n">
-        <v>-27</v>
+        <v>-25</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
       </c>
-      <c r="AN8" s="3" t="n">
-        <v>0.02141983290559235</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>0.04352494315082356</v>
-      </c>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10167,30 +10160,30 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>88</v>
+        <v>513</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>-0.001622802338923757</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>-0.09226300542917365</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>0.01496998077824432</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>46021</v>
+        <v>45707</v>
       </c>
       <c r="T9" t="b">
         <v>1</v>
@@ -10203,10 +10196,10 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-34</v>
+        <v>-195</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0</v>
+        <v>-0.001622802338923757</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>0</v>
@@ -10218,7 +10211,7 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-55</v>
+        <v>-220</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
@@ -10227,13 +10220,13 @@
         <v>0</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.06729733840789669</v>
+        <v>-0.1466145071230273</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.2051728224903451</v>
+        <v>0.3438573944579025</v>
       </c>
       <c r="AH9" t="n">
-        <v>-72</v>
+        <v>-167</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -10243,10 +10236,10 @@
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="n">
-        <v>0.1157245680572492</v>
+        <v>0.1149306197576361</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.08904827568122387</v>
+        <v>-0.1029587147715519</v>
       </c>
     </row>
     <row r="10">
@@ -10296,34 +10289,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>45124</v>
+      </c>
+      <c r="M10" t="n">
+        <v>384</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="P10" t="n">
+        <v>383</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.1314887237303285</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.09208397247949054</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45866</v>
-      </c>
-      <c r="M10" t="n">
-        <v>109</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="P10" t="n">
-        <v>108</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.06821577159885669</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.0484565948035845</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -10333,61 +10326,61 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AC10" t="n">
-        <v>20</v>
+        <v>-31</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.1822068127687015</v>
+        <v>0.3117521209239831</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.01884074360431218</v>
+        <v>-0.0545305346435368</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.05104850955225826</v>
+        <v>0.1078193491784604</v>
       </c>
       <c r="AH10" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>-0.001873098514625984</v>
+        <v>-1.70577183439824e-05</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-27</v>
+        <v>-5</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>0.1157245680572492</v>
+        <v>0.1149306197576361</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>-0.005987636340689106</v>
+        <v>-0.01368747521540192</v>
       </c>
     </row>
   </sheetData>
@@ -10401,7 +10394,1408 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AO10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>peak_date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>trough_date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>recovery_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_days</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_anchored_dd</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_hwm_dd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_days_underwater</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>full_no_drawdown</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>full_not_recovered</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days_vs_defined</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_depth</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_trough_at_boundary</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days_vs_bench</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_vs_bench_censored</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_return_to_even</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base_ulcer</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base_depth</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_days</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_censored</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb_ulcer</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb_depth</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_days</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_censored</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="M2" t="n">
+        <v>89</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="P2" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.06633642004451831</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>34</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0.2889940469367012</v>
+      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45861</v>
+      </c>
+      <c r="M3" t="n">
+        <v>106</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.2051728224903451</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.2051728224903451</v>
+      </c>
+      <c r="P3" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.09605815620571079</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.06729733840789669</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>34</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>-0.2051728224903451</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>-0.2051728224903451</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>72</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0.2581351371667873</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="M4" t="n">
+        <v>136</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="P4" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.06348808787815403</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.05032969331821049</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>34</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>102</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>47</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>0.1822068127687015</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>-0.0169676450896862</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>0.05104850955225826</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>89</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T5" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>-0.06729733840789669</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>0.2051728224903451</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-72</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.1157245680572492</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.08904827568122387</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="M6" t="n">
+        <v>136</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="P6" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.06348808787815403</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.05032969331821049</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>34</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>102</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>47</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>0.1822068127687015</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>-0.0169676450896862</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>0.05104850955225826</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="3" t="n">
+        <v>0.1157245680572492</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>-0.005987636340689106</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>89</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T7" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>-0.06729733840789669</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>0.2051728224903451</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-72</v>
+      </c>
+      <c r="AI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" s="3" t="n">
+        <v>0.02141983290559235</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>-0.01602903048447502</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="M8" t="n">
+        <v>109</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="P8" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.06821577159885669</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.0484565948035845</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>34</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0.1822068127687015</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>-0.01884074360431218</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0.05104850955225826</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3" t="n">
+        <v>-0.001873098514625984</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AM8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="3" t="n">
+        <v>0.02141983290559235</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>0.04352494315082356</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>89</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T9" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>-0.06729733840789669</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>0.2051728224903451</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-72</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.1157245680572492</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.08904827568122387</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="M10" t="n">
+        <v>109</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="P10" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.06821577159885669</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.0484565948035845</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>34</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="AA10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="3" t="n">
+        <v>0.1822068127687015</v>
+      </c>
+      <c r="AF10" s="3" t="n">
+        <v>-0.01884074360431218</v>
+      </c>
+      <c r="AG10" s="3" t="n">
+        <v>0.05104850955225826</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="3" t="n">
+        <v>-0.001873098514625984</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AM10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="3" t="n">
+        <v>0.1157245680572492</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>-0.005987636340689106</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10507,24 +11901,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>23</v>
+      </c>
       <c r="J2" s="3" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -10555,20 +11947,20 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-131</v>
+        <v>196</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="3" t="n">
-        <v>0.7281976744186046</v>
+        <v>0.473655019412091</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -10602,23 +11994,23 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-120</v>
+        <v>-131</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-57</v>
+        <v>523</v>
       </c>
       <c r="G4" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="3" t="n">
-        <v>0.04137931034482759</v>
+        <v>0.7281976744186046</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -10648,19 +12040,21 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="n">
+        <v>-119</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>-57</v>
+      </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.04794520547945205</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -10693,24 +12087,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>-132</v>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>0.3625730994152047</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -10741,21 +12133,23 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>-132</v>
+      </c>
       <c r="G7" t="n">
-        <v>94</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>1</v>
+        <v>0.3625730994152047</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -10772,37 +12166,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>259</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>59</v>
-      </c>
+        <v>-94</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" s="3" t="n">
-        <v>0.1058171745152355</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -10829,27 +12221,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>23</v>
+      </c>
       <c r="J9" s="3" t="n">
-        <v>0.3204941860465116</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -10876,25 +12266,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>258</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>59</v>
+      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
+        <v>0.1059345535219079</v>
+      </c>
+      <c r="K10" t="n">
         <v>6</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0.4206896551724138</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -10921,25 +12313,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3204941860465116</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -10966,24 +12360,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>119</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -11013,27 +12405,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>58</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
       <c r="J13" s="3" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -11050,24 +12440,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -11077,10 +12467,10 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" s="3" t="n">
-        <v>0.313573407202216</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -11097,37 +12487,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>59</v>
+        <v>-30</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>0.4585755813953488</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -11154,25 +12544,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.4206896551724138</v>
-      </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -11199,25 +12591,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>183</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3139212423738214</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -11244,27 +12638,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-63</v>
+        <v>59</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="G18" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="3" t="n">
-        <v>0.7309941520467836</v>
+        <v>0.4585755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -11291,32 +12685,169 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>58</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="3" t="n">
-        <v>1</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-63</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="G21" t="n">
+        <v>63</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
+        <v>0.7309941520467836</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-94</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="G22" t="n">
+        <v>94</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
